--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-perf-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/danhgianangluc/tester-perf-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Nếu không có Timers, các virtual users của JMeter sẽ gửi request liên tiếp ngay khi nhận được response (tốc độ của robot). Điều này tạo ra mức tải cực kỳ khốc liệt và phi thực tế. Chèn Timers (Think Time) giúp mô phỏng chính xác nhịp điệu tương tác của con người (đọc trang mất 3-5s rồi mới click), giúp kết quả đo lường tải sát với thực tế vận hành.</v>
       </c>
       <c r="F2" t="str">
-        <v>Sử dụng các bộ tạo thời gian trễ (Timers - như Uniform Random Timer hoặc Constant Timer) chèn vào giữa các Samplers để giả lập thời gian nghỉ ngẫu nhiên của người dùng — sử dụng JMeter Timers giả lập Think Time</v>
+        <v>Yêu cầu lập trình viên Frontend lập trình cho trang web tự động tải chậm đi 5 giây đối với tất cả các click chuột — làm chậm trang web</v>
       </c>
       <c r="G2" t="str">
-        <v>Yêu cầu lập trình viên Frontend lập trình cho trang web tự động tải chậm đi 5 giây đối với tất cả các click chuột — làm chậm trang web</v>
+        <v>Cấu hình cho máy chạy test tự động tắt kết nối mạng internet trong vòng 3 giây sau mỗi click chuột — ngắt kết nối mạng</v>
       </c>
       <c r="H2" t="str">
         <v>Chỉ chạy bộ kịch bản test hiệu năng với duy nhất 1 người dùng ảo trong toàn bộ phiên chạy — chạy đơn người dùng</v>
       </c>
       <c r="I2" t="str">
-        <v>Cấu hình cho máy chạy test tự động tắt kết nối mạng internet trong vòng 3 giây sau mỗi click chuột — ngắt kết nối mạng</v>
+        <v>Sử dụng các bộ tạo thời gian trễ (Timers - như Uniform Random Timer hoặc Constant Timer) chèn vào giữa các Samplers để giả lập thời gian nghỉ ngẫu nhiên của người dùng — sử dụng JMeter Timers giả lập Think Time</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>Điểm mà tại đó số lượng người dùng (VUs) tiếp tục tăng nhưng thông lượng (Throughput) đi ngang hoặc giảm, đồng thời thời gian phản hồi (Response Time) bắt đầu tăng vọt tuyến tính; biểu thị giới hạn chịu tải tối đa của hệ thống — bão hòa thông lượng tăng vọt phản hồi</v>
       </c>
       <c r="G3" t="str">
-        <v>Điểm mà tại đó dung lượng ổ cứng vật lý của máy chủ cơ sở dữ liệu bị đầy 100% — đầy ổ cứng</v>
+        <v>Điểm mà tại đó lập trình viên hoàn thành việc viết code 100% các tính năng nghiệp vụ — hoàn thành code</v>
       </c>
       <c r="H3" t="str">
         <v>Điểm mà tại đó số lượng lỗi (Bugs) được phát hiện trong ngày bằng đúng số lượng bug được sửa — bão hòa lỗi</v>
       </c>
       <c r="I3" t="str">
-        <v>Điểm mà tại đó lập trình viên hoàn thành việc viết code 100% các tính năng nghiệp vụ — hoàn thành code</v>
+        <v>Điểm mà tại đó dung lượng ổ cứng vật lý của máy chủ cơ sở dữ liệu bị đầy 100% — đầy ổ cứng</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -524,19 +524,19 @@
         <v>`EXPLAIN` là công cụ đắc lực của DBA/Tester để tuning hiệu năng. Nó chỉ ra database engine sẽ chạy thế nào: Quét tuần tự toàn bộ bảng (Seq Scan - cực chậm trên bảng lớn) hay Quét chỉ mục (Index Scan - cực nhanh). Nhờ đó, QA biết được cần tạo index ở cột nào hoặc viết lại câu lệnh JOIN.</v>
       </c>
       <c r="F4" t="str">
-        <v>Hiển thị kế hoạch thực thi truy vấn (Query Execution Plan) của công cụ tối ưu hóa, chỉ ra các bước quét toàn bảng (Table Scan/Seq Scan) do thiếu Index hoặc thực hiện phép JOIN không tối ưu — hiển thị kế hoạch thực thi định vị quét bảng</v>
+        <v>Tự động chia tách bảng dữ liệu lớn ra thành 10 bảng nhỏ độc lập trên ổ cứng — tự động chia tách bảng</v>
       </c>
       <c r="G4" t="str">
         <v>Tự động sửa chữa các lỗi cú pháp viết sai chính tả của câu lệnh SQL đó — tự sửa lỗi SQL</v>
       </c>
       <c r="H4" t="str">
+        <v>Hiển thị kế hoạch thực thi truy vấn (Query Execution Plan) của công cụ tối ưu hóa, chỉ ra các bước quét toàn bảng (Table Scan/Seq Scan) do thiếu Index hoặc thực hiện phép JOIN không tối ưu — hiển thị kế hoạch thực thi định vị quét bảng</v>
+      </c>
+      <c r="I4" t="str">
         <v>Mã hóa toàn bộ các bản ghi kết quả trả về của câu lệnh SQL đó để bảo mật thông tin tài chính — mã hóa kết quả SQL</v>
       </c>
-      <c r="I4" t="str">
-        <v>Tự động chia tách bảng dữ liệu lớn ra thành 10 bảng nhỏ độc lập trên ổ cứng — tự động chia tách bảng</v>
-      </c>
       <c r="J4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Hệ thống có cache chạy rất nhanh (Response Time &lt; 10ms) vì không phải truy vấn DB. Nhưng nếu cache bị hết hạn đồng loạt (Cache Stampede), hàng nghìn requests sẽ chọc thẳng xuống DB cùng lúc, dễ làm sập DB. Kịch bản test sập cache giúp đánh giá khả năng phòng vệ của DB (như cơ chế mutex lock, rate limiting).</v>
       </c>
       <c r="F5" t="str">
+        <v>Chỉ chạy test hiệu năng khi hệ thống Redis Cache hoạt động ổn định và không bao giờ được phép tắt cache — test khi có cache ổn định</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Tăng dung lượng bộ nhớ RAM của máy chủ chứa Redis Cache lên gấp 100 lần để đảm bảo không bao giờ hết hạn — nâng cấp RAM cực đoan</v>
+      </c>
+      <c r="H5" t="str">
         <v>Thiết kế kịch bản kiểm thử tải đột biến (Spike test) đồng thời xóa sạch cache (Flush cache) để ép toàn bộ các yêu cầu của người dùng chọc thẳng xuống cơ sở dữ liệu chính (DB), đo lường khả năng chịu tải của DB — giả lập sập cache đo lường sức chịu tải DB</v>
       </c>
-      <c r="G5" t="str">
-        <v>Chỉ chạy test hiệu năng khi hệ thống Redis Cache hoạt động ổn định và không bao giờ được phép tắt cache — test khi có cache ổn định</v>
-      </c>
-      <c r="H5" t="str">
+      <c r="I5" t="str">
         <v>Yêu cầu lập trình viên viết code xóa bỏ hoàn toàn cơ chế lưu bộ nhớ đệm để hệ thống chạy đơn giản hơn — loại bỏ cache</v>
       </c>
-      <c r="I5" t="str">
-        <v>Tăng dung lượng bộ nhớ RAM của máy chủ chứa Redis Cache lên gấp 100 lần để đảm bảo không bao giờ hết hạn — nâng cấp RAM cực đoan</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -588,19 +588,19 @@
         <v>Thiết kế sai mô hình tải sẽ cho kết quả test vô giá trị. Với website E-commerce public, người dùng truy cập ngẫu nhiên (Open model). Nếu server bị chậm, người dùng mới vẫn tiếp tục vào tạo request mới, làm hàng đợi phình to và sập server nhanh hơn. Closed model (như trong JMeter mặc định dùng thread group truyền thống) giới hạn số VUs cố định, nếu server chậm thì robot cũng gửi request chậm lại, làm giảm tải ảo lên server.</v>
       </c>
       <c r="F6" t="str">
+        <v>Closed chạy nhanh hơn Open gấp 10 lần do không tốn tài nguyên giả lập tải — so sánh hiệu năng tốc độ</v>
+      </c>
+      <c r="G6" t="str">
         <v>Closed: Số lượng người dùng hoạt động cố định, request mới chỉ gửi sau khi nhận response cũ (thích hợp hệ thống nội bộ ERP); Open: Request mới gửi đến theo phân phối ngẫu nhiên (như Poisson) bất kể người dùng trước đã nhận response chưa (thích hợp Web bán lẻ/E-commerce public) — Closed người dùng cố định vs Open request ngẫu nhiên liên tục</v>
       </c>
-      <c r="G6" t="str">
+      <c r="H6" t="str">
         <v>Closed chỉ áp dụng cho kiểm thử tự động; Open chỉ áp dụng cho kiểm thử thủ công — phân loại phương pháp test</v>
       </c>
-      <c r="H6" t="str">
+      <c r="I6" t="str">
         <v>Closed bắt buộc phải đóng toàn bộ các cổng kết nối mạng; Open yêu cầu mở toàn bộ cổng mạng — cơ chế bảo mật cổng mạng</v>
       </c>
-      <c r="I6" t="str">
-        <v>Closed chạy nhanh hơn Open gấp 10 lần do không tốn tài nguyên giả lập tải — so sánh hiệu năng tốc độ</v>
-      </c>
       <c r="J6">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -623,10 +623,10 @@
         <v>Làm tăng vọt thời gian phản hồi (Response Time) và gây lỗi treo cứng (Deadlock); QA thiết kế kịch bản test song song (Concurrency test) cho hàng trăm người dùng ảo cùng thực hiện cập nhật số dư của đúng một tài khoản ngân hàng cùng một lúc — test song song đồng thời phát hiện tranh chấp khóa</v>
       </c>
       <c r="G7" t="str">
+        <v>Làm cho hệ thống tự động đổi kiểu dữ liệu của cột khóa ngoại từ int sang string; QA chạy test kiểm tra kiểu dữ liệu — thay đổi kiểu dữ liệu</v>
+      </c>
+      <c r="H7" t="str">
         <v>Làm tăng dung lượng file sao lưu database lên gấp đôi; QA thiết kế kịch bản sao lưu dữ liệu hàng ngày — ảnh hưởng sao lưu</v>
-      </c>
-      <c r="H7" t="str">
-        <v>Làm cho hệ thống tự động đổi kiểu dữ liệu của cột khóa ngoại từ int sang string; QA chạy test kiểm tra kiểu dữ liệu — thay đổi kiểu dữ liệu</v>
       </c>
       <c r="I7" t="str">
         <v>Lập tức làm sập nguồn điện của toàn bộ hệ thống máy chủ vật lý chứa database; QA diễn tập mất điện — sập nguồn máy chủ</v>
@@ -652,19 +652,19 @@
         <v>Một máy tính cá nhân (JMeter Master) thường chỉ giả lập được tối đa 1,000 - 2,000 VUs tùy thuộc vào độ phức tạp của script. Để giả lập 50k VUs, ta phải dùng mô hình phân tán (Distributed), dùng nhiều máy Slave (Injectors) bơm tải đồng loạt. Sự đồng bộ thời gian (NTP clock sync) và băng thông mạng không bị nghẽn giữa Master-Slave là chìa khóa để thu thập dữ liệu tải chính xác.</v>
       </c>
       <c r="F8" t="str">
+        <v>Yêu cầu tất cả các máy Slave bắt buộc phải chạy hệ điều hành macOS phiên bản mới nhất — yêu cầu hệ điều hành Slave</v>
+      </c>
+      <c r="G8" t="str">
+        <v>Đảm bảo rằng máy Master tự động tắt nguồn điện của tất cả các máy Slave ngay khi chạy test xong — tắt nguồn máy Slave</v>
+      </c>
+      <c r="H8" t="str">
         <v>Thiết lập 1 máy Master điều phối và nhiều máy Slave trực tiếp bơm tải để tránh quá tải CPU/băng thông mạng của máy Master; lưu ý quan trọng nhất là các máy Slave phải nằm trong cùng mạng LAN hoặc kết nối mạng có độ trễ cực thấp và không bị chặn tường lửa các port điều khiển — Master-Slave phân tán tải và đồng bộ mạng LAN</v>
       </c>
-      <c r="G8" t="str">
+      <c r="I8" t="str">
         <v>Thiết lập để các máy Slave tự động mã hóa dữ liệu chạy test bằng thuật toán bảo mật MD5 trước khi gửi về Master — mã hóa dữ liệu truyền</v>
       </c>
-      <c r="H8" t="str">
-        <v>Yêu cầu tất cả các máy Slave bắt buộc phải chạy hệ điều hành macOS phiên bản mới nhất — yêu cầu hệ điều hành Slave</v>
-      </c>
-      <c r="I8" t="str">
-        <v>Đảm bảo rằng máy Master tự động tắt nguồn điện của tất cả các máy Slave ngay khi chạy test xong — tắt nguồn máy Slave</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Hệ thống bất đồng bộ trả về HTTP 202 Accepted ngay khi nhận tin nhắn vào queue (Response Time &lt; 5ms). Tuy nhiên, tin nhắn có thể mất 10s xếp hàng và xử lý ở phía sau. Sử dụng Correlation ID kết hợp công cụ Distributed Tracing (như Jaeger, Zipkin) hoặc quét DB/log đối chiếu timestamp là cách duy nhất để đo lường chính xác thời gian xử lý thực tế của nghiệp vụ (End-to-End Processing Time).</v>
       </c>
       <c r="F9" t="str">
+        <v>Chỉ đo thời gian từ lúc gửi tin nhắn vào queue cho đến khi nhận được xác nhận thành công (ACK) của hàng đợi — chỉ đo thời gian gửi queue</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Yêu cầu lập trình viên tạm thời chuyển toàn bộ kiến trúc bất đồng bộ sang kiến trúc gọi API đồng bộ để dễ dàng đo lường — chuyển sang đồng bộ</v>
+      </c>
+      <c r="H9" t="str">
         <v>Sử dụng mã định danh giao dịch duy nhất (Correlation ID) đính kèm vào tin nhắn, ghi lại timestamp tại thời điểm bắt đầu gửi vào queue và timestamp tại thời điểm service cuối cùng xử lý xong lưu trong database/log, sau đó đối chiếu chênh lệch — theo dõi Correlation ID và đối chiếu timestamp</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Chỉ đo thời gian từ lúc gửi tin nhắn vào queue cho đến khi nhận được xác nhận thành công (ACK) của hàng đợi — chỉ đo thời gian gửi queue</v>
-      </c>
-      <c r="H9" t="str">
-        <v>Yêu cầu lập trình viên tạm thời chuyển toàn bộ kiến trúc bất đồng bộ sang kiến trúc gọi API đồng bộ để dễ dàng đo lường — chuyển sang đồng bộ</v>
       </c>
       <c r="I9" t="str">
         <v>Chạy thử nghiệm kịch bản test hiệu năng thủ công bằng cách sử dụng đồng hồ bấm giờ trên tay để đo — đo thủ công bấm giờ</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Khi JOIN bảng A (1 triệu dòng) và bảng B (1 triệu dòng) qua cột không có index, DB phải so sánh từng dòng của bảng A với từng dòng của bảng B (Nested Loop), tốn $10^{12}$ phép so sánh. Có index giúp DB tra cứu trực tiếp cực nhanh. Khác biệt kiểu dữ liệu (ví dụ JOIN cột VARCHAR với INT) cũng vô hiệu hóa index do DB phải chạy hàm ép kiểu ngầm (Implicit Conversion).</v>
       </c>
       <c r="F10" t="str">
-        <v>Vì database engine phải thực hiện quét toàn bảng (Full Table Scan) kết hợp thuật toán Hash Join/Nested Loop trên ổ cứng cực kỳ chậm; QA phát hiện bằng cách chạy EXPLAIN kế hoạch thực thi và quan sát thời gian phản hồi tăng lên theo cấp số nhân khi kích thước bảng tăng — quét toàn bảng do thiếu index JOIN</v>
+        <v>Vì phép JOIN không index bắt buộc hệ quản trị cơ sở dữ liệu phải chuyển đổi dữ liệu sang định dạng file Excel — chuyển sang file Excel</v>
       </c>
       <c r="G10" t="str">
         <v>Vì database sẽ tự động xóa bỏ các cột dữ liệu không có index để giải phóng bộ nhớ RAM của máy chủ — tự động xóa cột</v>
       </c>
       <c r="H10" t="str">
-        <v>Vì phép JOIN không index bắt buộc hệ quản trị cơ sở dữ liệu phải chuyển đổi dữ liệu sang định dạng file Excel — chuyển sang file Excel</v>
+        <v>Vì nó làm sập card màn hình của máy tính người dùng khi hiển thị kết quả truy vấn — sập card màn hình</v>
       </c>
       <c r="I10" t="str">
-        <v>Vì nó làm sập card màn hình của máy tính người dùng khi hiển thị kết quả truy vấn — sập card màn hình</v>
+        <v>Vì database engine phải thực hiện quét toàn bảng (Full Table Scan) kết hợp thuật toán Hash Join/Nested Loop trên ổ cứng cực kỳ chậm; QA phát hiện bằng cách chạy EXPLAIN kế hoạch thực thi và quan sát thời gian phản hồi tăng lên theo cấp số nhân khi kích thước bảng tăng — quét toàn bảng do thiếu index JOIN</v>
       </c>
       <c r="J10">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -748,10 +748,10 @@
         <v>Định vị Bottleneck yêu cầu bức tranh toàn cảnh. APM Tools giúp phân tích sâu (profiling): Nếu CPU database 100%, lỗi ở DB (thiếu index, khóa transaction). Nếu CPU app server 100% nhưng DB rảnh, lỗi ở code (thuật toán tồi, vô hạn lặp, nghẽn thread pool). Nếu cả hai rảnh nhưng Response Time cao, lỗi ở mạng (network latency) hoặc nghẽn cổng kết nối bên thứ ba.</v>
       </c>
       <c r="F11" t="str">
+        <v>Chỉ cần kiểm tra xem tốc độ đường truyền internet của máy chạy test có đạt mức 100Mbps hay không — kiểm tra tốc độ internet client</v>
+      </c>
+      <c r="G11" t="str">
         <v>Phân tích chỉ số tài nguyên hệ thống đồng thời (APM Tools - Application Performance Monitoring như NewRelic, Dynatrace): Theo dõi CPU/RAM sử dụng của từng máy chủ, tốc độ truy vấn SQL, thời gian khóa database lock, và thời gian trễ mạng truyền dẫn — giám sát đa tầng APM định vị Bottleneck</v>
-      </c>
-      <c r="G11" t="str">
-        <v>Chỉ cần kiểm tra xem tốc độ đường truyền internet của máy chạy test có đạt mức 100Mbps hay không — kiểm tra tốc độ internet client</v>
       </c>
       <c r="H11" t="str">
         <v>Sa thải lập trình viên Frontend và tuyển dụng lập trình viên Backend mới để cải tiến hiệu năng code — sa thải nhân sự frontend</v>
@@ -760,7 +760,7 @@
         <v>Tắt toàn bộ hệ thống máy chủ và khởi động lại từ đầu để xem hệ thống có chạy nhanh hơn không — khởi động lại máy chủ đơn thuần</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
